--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -113,10 +118,19 @@
     <t>75000,1000,1000,3</t>
   </si>
   <si>
-    <t>防御</t>
+    <t>金币</t>
   </si>
   <si>
     <t>小女道士</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>爆率</t>
   </si>
   <si>
     <t>Tap玩家</t>
@@ -1425,7 +1439,7 @@
         <v>5003</v>
       </c>
       <c r="L10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>28</v>
@@ -1468,22 +1482,53 @@
       <c r="L11" s="1">
         <v>20</v>
       </c>
+      <c r="M11" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" customHeight="1" spans="1:13">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="L12" s="1">
+        <v>20</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="L13" s="1">
+        <v>20</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
       <c r="F14" s="1"/>
@@ -1618,7 +1663,7 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
@@ -1627,10 +1672,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I37" s="1">
         <v>1001</v>
@@ -1650,7 +1695,7 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -1659,10 +1704,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I38" s="1">
         <v>1002</v>
@@ -1682,7 +1727,7 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -1691,10 +1736,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I39" s="1">
         <v>1003</v>
@@ -1714,7 +1759,7 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -1723,10 +1768,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I40" s="1">
         <v>2003</v>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -109,31 +109,40 @@
     <t>生命</t>
   </si>
   <si>
-    <t>小男道士</t>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>10001,85,81,92</t>
+  </si>
+  <si>
+    <t>3,30,10,6</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>10001,86,82,92</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>10001,10002,83,92</t>
+  </si>
+  <si>
+    <t>3,3,5,6</t>
+  </si>
+  <si>
+    <t>爆率</t>
+  </si>
+  <si>
+    <t>10001,10002,84,92</t>
+  </si>
+  <si>
+    <t>Tap玩家</t>
   </si>
   <si>
     <t>1,2,3,92</t>
-  </si>
-  <si>
-    <t>75000,1000,1000,3</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>小女道士</t>
-  </si>
-  <si>
-    <t>经验</t>
-  </si>
-  <si>
-    <t>品质</t>
-  </si>
-  <si>
-    <t>爆率</t>
-  </si>
-  <si>
-    <t>Tap玩家</t>
   </si>
   <si>
     <t>10000,200,200,1</t>
@@ -1405,12 +1414,6 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1430,39 +1433,33 @@
         <v>27</v>
       </c>
       <c r="I10" s="1">
-        <v>1002</v>
+        <v>81</v>
       </c>
       <c r="J10" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1">
         <v>5003</v>
       </c>
       <c r="L10" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>27</v>
@@ -1471,63 +1468,93 @@
         <v>27</v>
       </c>
       <c r="I11" s="1">
-        <v>1003</v>
+        <v>82</v>
       </c>
       <c r="J11" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K11" s="1">
         <v>5003</v>
       </c>
       <c r="L11" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:13">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="1">
+        <v>83</v>
+      </c>
+      <c r="J12" s="1">
+        <v>5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>5003</v>
+      </c>
       <c r="L12" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="D13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="1">
+        <v>84</v>
+      </c>
+      <c r="J13" s="1">
+        <v>5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>5003</v>
+      </c>
       <c r="L13" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -1663,19 +1690,19 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I37" s="1">
         <v>1001</v>
@@ -1695,19 +1722,19 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I38" s="1">
         <v>1002</v>
@@ -1727,19 +1754,19 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I39" s="1">
         <v>1003</v>
@@ -1759,19 +1786,19 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I40" s="1">
         <v>2003</v>
